--- a/business_surveys/023_expense_forecast_reliability_survey--business_surveys.xlsx
+++ b/business_surveys/023_expense_forecast_reliability_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_41,_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 41, 'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_42,_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 42, 'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_43,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 43, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_53,_'value':_'$100,000-$200,000'}</t>
+          <t>$100,000-$200,000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 53, 'value': '$100,000-$200,000'}</t>
+          <t>$100,000-$200,000</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_61,_'value':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 61, 'value': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_62,_'value':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 62, 'value': 'Self-Employed'}</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_63,_'value':_'consultant'}</t>
+          <t>consultant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 63, 'value': 'Consultant'}</t>
+          <t>Consultant</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_64,_'value':_'retiree'}</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 64, 'value': 'Retiree'}</t>
+          <t>Retiree</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_71,_'value':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 71, 'value': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_72,_'value':_'healthcare'}</t>
+          <t>healthcare</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 72, 'value': 'Healthcare'}</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_73,_'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 73, 'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_74,_'value':_'creative'}</t>
+          <t>creative</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 74, 'value': 'Creative'}</t>
+          <t>Creative</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_91,_'value':_'always_accurate'}</t>
+          <t>always_accurate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 91, 'value': 'Always accurate'}</t>
+          <t>Always accurate</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_92,_'value':_'sometimes_accurate'}</t>
+          <t>sometimes_accurate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 92, 'value': 'Sometimes accurate'}</t>
+          <t>Sometimes accurate</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_93,_'value':_'rarely_accurate'}</t>
+          <t>rarely_accurate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 93, 'value': 'Rarely accurate'}</t>
+          <t>Rarely accurate</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_94,_'value':_'never_accurate'}</t>
+          <t>never_accurate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 94, 'value': 'Never accurate'}</t>
+          <t>Never accurate</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_101,_'value':_'always_accurate'}</t>
+          <t>always_accurate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 101, 'value': 'Always accurate'}</t>
+          <t>Always accurate</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_102,_'value':_'sometimes_accurate'}</t>
+          <t>sometimes_accurate</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 102, 'value': 'Sometimes accurate'}</t>
+          <t>Sometimes accurate</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_102,_'value':_'rarely_accurate'}</t>
+          <t>rarely_accurate</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 102, 'value': 'Rarely accurate'}</t>
+          <t>Rarely accurate</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_103,_'value':_'never_accurate'}</t>
+          <t>never_accurate</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 103, 'value': 'Never accurate'}</t>
+          <t>Never accurate</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_111,_'value':_'always_accurate'}</t>
+          <t>always_accurate</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 111, 'value': 'Always accurate'}</t>
+          <t>Always accurate</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_112,_'value':_'sometimes_accurate'}</t>
+          <t>sometimes_accurate</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 112, 'value': 'Sometimes accurate'}</t>
+          <t>Sometimes accurate</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_112,_'value':_'rarely_accurate'}</t>
+          <t>rarely_accurate</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 112, 'value': 'Rarely accurate'}</t>
+          <t>Rarely accurate</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_113,_'value':_'never_accurate'}</t>
+          <t>never_accurate</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 113, 'value': 'Never accurate'}</t>
+          <t>Never accurate</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_131,_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 131, 'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_132,_'value':_'less_than_3_times_a_month'}</t>
+          <t>less_than_3_times_a_month</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 132, 'value': 'Less than 3 times a month'}</t>
+          <t>Less than 3 times a month</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_133,_'value':_'more_than_3_times_a_month'}</t>
+          <t>more_than_3_times_a_month</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 133, 'value': 'More than 3 times a month'}</t>
+          <t>More than 3 times a month</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_171,_'value':_'highly_accurate'}</t>
+          <t>highly_accurate</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 171, 'value': 'Highly accurate'}</t>
+          <t>Highly accurate</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_172,_'value':_'somewhat_accurate'}</t>
+          <t>somewhat_accurate</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 172, 'value': 'Somewhat accurate'}</t>
+          <t>Somewhat accurate</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_173,_'value':_'not_very_accurate'}</t>
+          <t>not_very_accurate</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 173, 'value': 'Not very accurate'}</t>
+          <t>Not very accurate</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_181,_'value':_'highly_accurate'}</t>
+          <t>highly_accurate</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 181, 'value': 'Highly accurate'}</t>
+          <t>Highly accurate</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_182,_'value':_'somewhat_accurate'}</t>
+          <t>somewhat_accurate</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 182, 'value': 'Somewhat accurate'}</t>
+          <t>Somewhat accurate</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_182,_'value':_'not_very_accurate'}</t>
+          <t>not_very_accurate</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 182, 'value': 'Not very accurate'}</t>
+          <t>Not very accurate</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_183,_'value':_'not_at_all_accurate'}</t>
+          <t>not_at_all_accurate</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 183, 'value': 'Not at all accurate'}</t>
+          <t>Not at all accurate</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_191,_'value':_'highly_accurate'}</t>
+          <t>highly_accurate</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 191, 'value': 'Highly accurate'}</t>
+          <t>Highly accurate</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_192,_'value':_'somewhat_accurate'}</t>
+          <t>somewhat_accurate</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 192, 'value': 'Somewhat accurate'}</t>
+          <t>Somewhat accurate</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_192,_'value':_'not_very_accurate'}</t>
+          <t>not_very_accurate</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 192, 'value': 'Not very accurate'}</t>
+          <t>Not very accurate</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_193,_'value':_'not_at_all_accurate'}</t>
+          <t>not_at_all_accurate</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 193, 'value': 'Not at all accurate'}</t>
+          <t>Not at all accurate</t>
         </is>
       </c>
     </row>
